--- a/data/food_knowledge_dataset.xlsx
+++ b/data/food_knowledge_dataset.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foods_Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Substitutions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retailer_Prices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retailer_Prices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Substitutions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -9653,3504 +9653,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16.69921875" customWidth="1" min="1" max="1"/>
-    <col width="31.09765625" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="30.19921875" customWidth="1" min="4" max="4"/>
-    <col width="16.3984375" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.05" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>food_id</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>retailer_price</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>substitute_food_id</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>substitute_retailer_price</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>swap_realism</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>British Whole Milk</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>British Semi-Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>British Whole Milk</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>British Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>British Semi-Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>British Whole Milk</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>British Semi-Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>British Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>British Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>British Semi-Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>British Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>British Whole Milk</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>D14</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Unsweetened Soya Milk</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>British Whole Milk</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>D14</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Unsweetened Soya Milk</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>British Semi-Skimmed Milk</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Skyr Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Skyr Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Skyr Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Skyr Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Fat Free Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>D07</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Strawberry Yoghurt</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Low Fat Cottage Cheese</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Greek Style Yoghurt</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Low Fat Cottage Cheese</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Skyr Natural Yoghurt</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>British Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Lighter Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Lighter Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>British Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>British Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Lighter Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>British Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Lighter Mature Cheddar</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Mozzarella</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Breast Fillets</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Thigh Fillets</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Thigh Fillets</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Breast Fillets</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Breast Fillets</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>British Turkey Breast Steaks</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>British Turkey Breast Steaks</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Breast Fillets</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>British Chicken Thigh Fillets</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>British Turkey Breast Steaks</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>British Lean Beef Mince 5% Fat</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>British Lean Beef Mince 5% Fat</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>British Pork Mince</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>British Pork Mince</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>British Lean Beef Mince 5% Fat</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>British Pork Mince</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>British Pork Loin Chops</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>British Pork Mince</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>British Lamb Mince</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>British Lamb Mince</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>British Lean Beef Mince 5% Fat</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>British Beef Mince 20% Fat</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>British Lamb Mince</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Salmon Fillets</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Mackerel Fillets</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Mackerel Fillets</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Salmon Fillets</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Salmon Fillets</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Chunks in Spring Water</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Chunks in Spring Water</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Salmon Fillets</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Cod Fillets</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Haddock Fillets</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Haddock Fillets</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Cod Fillets</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Cod Fillets</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Tilapia Fillets</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Tilapia Fillets</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Cod Fillets</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Haddock Fillets</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Tilapia Fillets</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Chunks in Spring Water</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Cod Fillets</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cooked King Prawns</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Scottish Salmon Fillets</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Cooked King Prawns</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Chunks in Spring Water</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>British Free Range Eggs</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>P09</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>British Free Range Eggs</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Silken Tofu</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Silken Tofu</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Red Lentils</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Chickpeas</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Chickpeas</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Red Lentils</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Red Lentils</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Red Lentils</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Chickpeas</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Chickpeas</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Baked Beans</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Kidney Beans in Water</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Baked Beans</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Frozen Edamame Beans</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Firm Tofu</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Frozen Edamame Beans</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Frozen Edamame Beans</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Red Lentils</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Smooth Peanut Butter</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Walnut Halves</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Walnut Halves</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Cashew Nuts</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Cashew Nuts</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Walnut Halves</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Whole Hazelnuts</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Whole Hazelnuts</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Walnut Halves</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Mixed Nuts</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Whole Almonds</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Mixed Nuts</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Walnut Halves</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Easy Cook Long Grain White Rice</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Wholegrain Brown Rice</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Wholegrain Brown Rice</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Easy Cook Long Grain White Rice</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Short Grain Rice</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Easy Cook Long Grain White Rice</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Easy Cook Long Grain White Rice</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Short Grain Rice</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>White Bread</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Wholemeal Bread</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Wholemeal Bread</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>White Bread</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Rolled Porridge Oats</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>C08</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Pearl Barley</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>C08</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Pearl Barley</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>C09</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Bulgur Wheat</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>C09</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Bulgur Wheat</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>C08</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Pearl Barley</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>C06</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>White Potatoes</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Sweet Potatoes</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Sweet Potatoes</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>C06</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>White Potatoes</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>V05</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>V06</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Cauliflower</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>V06</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Cauliflower</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>V05</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>V05</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>V17</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Brussels Sprouts</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>V17</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Brussels Sprouts</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>V05</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>V06</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Cauliflower</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>V09</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Savoy Cabbage</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>V09</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Savoy Cabbage</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>V06</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Cauliflower</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>V07</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Baby Spinach</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>V08</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Kale</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>V08</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Kale</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>V07</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Baby Spinach</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>V07</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Baby Spinach</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>V10</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Iceberg Lettuce</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>V10</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Iceberg Lettuce</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>V07</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>Baby Spinach</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>V11</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Cucumber</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>V12</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>V04</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Cherry Tomatoes</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>V13</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Mixed Peppers</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>V13</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Mixed Peppers</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>V04</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Cherry Tomatoes</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>V12</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>V20</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Butternut Squash</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>V20</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Butternut Squash</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>V12</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Courgettes</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>V20</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Butternut Squash</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>V21</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Pumpkin</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>V21</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Pumpkin</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>V20</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>Butternut Squash</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Carrots</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Raw Beetroot</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Raw Beetroot</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>Carrots</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>V23</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Celeriac</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>V18</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Celery</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>V18</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Celery</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>V23</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>Celeriac</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>V15</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>Fine Green Beans</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>V16</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Frozen Peas</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>V16</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>Frozen Peas</t>
-        </is>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>V15</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
-        <is>
-          <t>Fine Green Beans</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>V03</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>Brown Onions</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>V18</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Celery</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Strawberries</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>F06</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>Blueberries</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>F06</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Blueberries</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Strawberries</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>F22</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Raspberries</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>Strawberries</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>Strawberries</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>F22</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Raspberries</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>F22</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Raspberries</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>F23</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>Blackberries</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>F23</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>Blackberries</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>F22</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Raspberries</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>F06</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Blueberries</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>F22</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>Raspberries</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>Easy Peel Oranges</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>F20</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Grapefruit</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>F20</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>Grapefruit</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Easy Peel Oranges</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>F13</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>Lemons</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>F14</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Limes</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>F14</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Limes</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>F13</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Lemons</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Gala Apples</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>F04</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Conference Pears</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>F04</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>Conference Pears</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Gala Apples</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>F15</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>Peaches</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>F16</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Plums</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>F16</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>Plums</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>F15</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Peaches</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>F15</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>Peaches</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>F18</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Apricots</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>F18</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>Apricots</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>F15</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>Peaches</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>F17</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Cherries</t>
-        </is>
-      </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>F19</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Pomegranate</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>F02</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>F09</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Mango</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>F09</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>Mango</t>
-        </is>
-      </c>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>F08</t>
-        </is>
-      </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Pineapple</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>F08</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>Pineapple</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
-        <is>
-          <t>F09</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Mango</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>Kiwi Fruit</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Easy Peel Oranges</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>Watermelon</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>F12</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Cantaloupe Melon</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>F12</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>Cantaloupe Melon</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>Watermelon</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>F21</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>Avocados</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>Smooth Peanut Butter</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>Smooth Peanut Butter</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>F21</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Avocados</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -20779,4 +17281,3027 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E120"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>food_id</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>substitute_food_id</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>swap_realism</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>swap_realism_label</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>swap_criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>P29</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>P29</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>P29</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Same nutritional role, different cooking style</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Requires different cooking method or habit</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Same nutritional role, different cooking style</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Requires different cooking method or habit</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>V17</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>V20</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>V21</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>V21</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>V20</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>V16</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>V16</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>V15</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Same meal context, small adjustment</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>Slight change but still very realistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>Drop-in replacement</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>No real change in cooking or usage</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>